--- a/input/old/Metadata _Alternative payee assigned to vendor_200025_001386.xlsx
+++ b/input/old/Metadata _Alternative payee assigned to vendor_200025_001386.xlsx
@@ -430,7 +430,7 @@
         <v>Updated on</v>
       </c>
       <c r="B7" t="str">
-        <v>16.01.2026 at 17:05 by ILIYAR</v>
+        <v>16.01.2026 at 17:05 by REDACTED</v>
       </c>
     </row>
     <row r="8">
